--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,12 +472,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>AB1024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,44 +492,131 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Låg Bloom-nivå</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>AS3024</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>HIA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Låg Bloom-nivå</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Låg Bloom-nivå</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Låg Bloom-nivå</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$6</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$6</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AB1024</t>
+          <t>AB1005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,130 +482,1804 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>AB1006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>9 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1006</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AS3024</t>
+          <t>AB1009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>5 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>AB1014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Låg Bloom-nivå</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
+          <t>4 av 12 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>AB1029</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [1,1,0,0,3,0]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AB3001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2NP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,1,0,1,1]</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2QB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,2,3,2]</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,1,0,1,1]</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GBQ36D</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3 av 9 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FI1028</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FI1031</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4 av 9 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FI1033</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4 av 9 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FI1038</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3 av 7 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GFI293</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>AHI263</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AHI26P</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AS3016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AS3022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AS3023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AS3024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7 av 16 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,3,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GLP234</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GLP2MU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GLP2QX</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GMN3EZ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,1,0,3]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>NA1003</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NA1026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>NA3007</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,7,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>NA3008</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4 av 4 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>PE1069</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hög verbnivå för grundkurs</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,0,0,2]</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>APG24S</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>APG27T</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>APG27U</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>APG27Z</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [12,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>APG282</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [8,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>APG28B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [10,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>APG28M</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>APG28R</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>APG28S</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EV</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3 av 13 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PG3069</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3 av 5 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ARK29H</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,3,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3 av 11 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>RV1009</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3 av 5 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>RV1015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3 av 6 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RV1037</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3 av 6 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4 av 11 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ASK22L</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [6,0,2,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3 av 10 bullets har okänt ledande verb</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ATR26B</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,1,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>AS3012</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Låg Bloom-nivå</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Avancerad kurs utan höga Bloom-verb (analysera/utvärdera/skapa…)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,0,1,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -617,6 +2291,130 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$E$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2012-02-27</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1005</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2012-02-27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>9 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1006</t>
         </is>
@@ -536,15 +568,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2010-04-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>5 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
         </is>
@@ -563,15 +601,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2011-04-12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>4 av 12 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
         </is>
@@ -590,15 +634,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [1,1,0,0,3,0]</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
@@ -617,15 +667,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2009-11-26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,1,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
@@ -644,15 +700,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B2</t>
         </is>
@@ -671,15 +733,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,1,0,1,1]</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2NP</t>
         </is>
@@ -698,15 +766,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,2,3,2]</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2QB</t>
         </is>
@@ -725,15 +799,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,1,0,1,1]</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U9</t>
         </is>
@@ -752,15 +832,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>3 av 9 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36D</t>
         </is>
@@ -779,15 +865,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>2010-02-16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>5 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
@@ -806,15 +902,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>2010-02-16</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>4 av 9 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1031</t>
         </is>
@@ -833,15 +939,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2010-02-16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2015-10-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>4 av 9 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1033</t>
         </is>
@@ -860,15 +976,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>4 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1038</t>
         </is>
@@ -887,15 +1013,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2011-05-30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>3 av 7 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
@@ -914,15 +1050,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2019-04-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>4 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI293</t>
         </is>
@@ -941,15 +1083,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI263</t>
         </is>
@@ -968,15 +1116,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,3,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI26P</t>
         </is>
@@ -995,15 +1149,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,2,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
@@ -1022,15 +1182,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3016</t>
         </is>
@@ -1049,15 +1215,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
@@ -1076,15 +1248,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
@@ -1103,15 +1285,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3023</t>
         </is>
@@ -1130,15 +1322,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3024</t>
         </is>
@@ -1157,15 +1359,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2007-05-30</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>7 av 16 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -1184,15 +1396,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2009-09-02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,3,0,0,0]</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
@@ -1211,15 +1429,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>2018-05-21</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
         </is>
@@ -1238,15 +1462,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
@@ -1265,15 +1495,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
@@ -1292,15 +1528,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2015-12-10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
@@ -1319,15 +1565,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,1,0,3]</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
@@ -1346,15 +1598,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2009-03-05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>5 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
@@ -1373,15 +1635,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>6 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
@@ -1400,15 +1668,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>4 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
@@ -1427,15 +1705,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>4 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
@@ -1454,15 +1738,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2007-09-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2008-02-07</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,7,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
@@ -1481,15 +1775,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>2007-09-05</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>4 av 4 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
         </is>
@@ -1508,15 +1808,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>2013-11-11</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,0,0,2]</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
@@ -1535,15 +1845,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
@@ -1562,15 +1882,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
@@ -1589,15 +1915,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
@@ -1616,15 +1948,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
@@ -1643,15 +1981,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [12,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
@@ -1670,15 +2014,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [8,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
@@ -1697,15 +2047,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [10,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
@@ -1724,15 +2080,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
@@ -1751,15 +2113,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
@@ -1778,15 +2146,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
@@ -1805,15 +2179,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>3 av 13 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
@@ -1832,15 +2212,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
@@ -1859,15 +2249,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,3,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
@@ -1886,15 +2282,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>3 av 11 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
@@ -1913,15 +2315,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>2007-01-10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
@@ -1940,15 +2348,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2007-04-04</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>3 av 6 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
@@ -1967,15 +2381,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>2008-06-10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>3 av 6 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
@@ -1994,15 +2414,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>2012-03-08</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>4 av 11 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
@@ -2021,15 +2447,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [6,0,2,0,0,0]</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
@@ -2048,15 +2484,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Okänt ledande verb</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>3 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
@@ -2075,15 +2517,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,1,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
@@ -2102,15 +2550,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
@@ -2129,15 +2587,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
@@ -2156,15 +2624,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>2015-06-17</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
@@ -2183,15 +2661,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
@@ -2210,15 +2694,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
@@ -2237,15 +2727,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,0,1,0,0,0]</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
@@ -2264,157 +2760,163 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Låg verbnivå för avancerad kurs</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E68"/>
+  <autoFilter ref="A1:G68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Bloom-taxonomi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bloom-taxonomi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloom-taxonomi'!$A$1:$G$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1419,7 +1419,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GLP234</t>
+          <t>GLP2MU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2018-05-21</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1440,19 +1440,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP234</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GLP2MU</t>
+          <t>GLP2QX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1478,14 +1478,14 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2MU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GLP2QX</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,10 +1495,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>2015-12-10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Hög verbnivå för grundkurs</t>
@@ -1506,36 +1510,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [0,1,0,0,0,2]</t>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2QX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>GMN3EZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2015-12-10</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Hög verbnivå för grundkurs</t>
@@ -1543,52 +1543,56 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [0,0,0,0,1,2]</t>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,1,0,3]</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMN3EZ</t>
+          <t>NA1003</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2009-03-05</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hög verbnivå för grundkurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,1,0,3]</t>
+          <t>5 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,14 +1602,10 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2006-12-06</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2009-03-05</t>
-        </is>
-      </c>
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Okänt ledande verb</t>
@@ -1613,19 +1613,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5 av 10 bullets har okänt ledande verb</t>
+          <t>6 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1638,7 +1638,11 @@
           <t>2009-10-19</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Okänt ledande verb</t>
@@ -1646,19 +1650,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6 av 10 bullets har okänt ledande verb</t>
+          <t>4 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,14 +1672,10 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2009-10-19</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2013-03-07</t>
-        </is>
-      </c>
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Okänt ledande verb</t>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>NA3007</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,30 +1705,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2006-12-06</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>2007-09-05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2008-02-07</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4 av 10 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,7,1,0,0,0]</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NA3007</t>
+          <t>NA3008</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1741,101 +1745,101 @@
           <t>2007-09-05</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2008-02-07</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,7,1,0,0,0]</t>
+          <t>4 av 4 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NA3008</t>
+          <t>PE1069</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2007-09-05</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>2013-11-11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Hög verbnivå för grundkurs</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4 av 4 bullets har okänt ledande verb</t>
+          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,0,0,2]</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PE1069</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2013-11-11</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2014-01-24</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hög verbnivå för grundkurs</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grundkurs domineras av värdera/skapa; fördelning [1,0,0,0,0,2]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,14 +1849,10 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2020-02-24</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Låg verbnivå för avancerad kurs</t>
@@ -1860,19 +1860,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2020-02-25</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1893,19 +1893,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1926,19 +1926,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1959,19 +1959,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [7,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [12,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1992,19 +1992,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [12,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [8,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2025,19 +2025,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [8,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [10,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2058,19 +2058,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [10,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2091,19 +2091,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [5,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2129,14 +2129,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2146,30 +2146,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [9,0,0,0,0,0]</t>
+          <t>3 av 13 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>PG3069</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,10 +2179,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2018-04-12</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Okänt ledande verb</t>
@@ -2190,56 +2194,52 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3 av 13 bullets har okänt ledande verb</t>
+          <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PG3069</t>
+          <t>ARK29H</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3 av 5 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,3,0,0,0,0]</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ARK29H</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2249,40 +2249,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [0,3,0,0,0,0]</t>
+          <t>3 av 11 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2293,19 +2293,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3 av 11 bullets har okänt ledande verb</t>
+          <t>3 av 5 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2007-04-04</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2326,19 +2326,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3 av 5 bullets har okänt ledande verb</t>
+          <t>3 av 6 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2007-04-04</t>
+          <t>2008-06-10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2008-06-10</t>
+          <t>2012-03-08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2392,135 +2392,139 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3 av 6 bullets har okänt ledande verb</t>
+          <t>4 av 11 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2012-03-08</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4 av 11 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [6,0,2,0,0,0]</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Låg verbnivå för avancerad kurs</t>
+          <t>Okänt ledande verb</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [6,0,2,0,0,0]</t>
+          <t>3 av 10 bullets har okänt ledande verb</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Okänt ledande verb</t>
+          <t>Låg verbnivå för avancerad kurs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3 av 10 bullets har okänt ledande verb</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,1,1,0,0,0]</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Låg verbnivå för avancerad kurs</t>
@@ -2528,19 +2532,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,1,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2565,19 +2569,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2015-06-17</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2602,19 +2606,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,1,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>AS3008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2624,14 +2628,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2015-06-17</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Låg verbnivå för avancerad kurs</t>
@@ -2639,19 +2639,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2677,14 +2677,14 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>AS4001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2705,19 +2705,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [4,0,0,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,0,1,0,0,0]</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2738,50 +2738,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [1,0,1,0,0,0]</t>
+          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Låg verbnivå för avancerad kurs</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Avancerad kurs utan analysera/värdera/skapa-verb; fördelning [3,0,0,0,0,0]</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G68"/>
+  <autoFilter ref="A1:G67"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2915,8 +2882,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
